--- a/tabelas/2026.xlsx
+++ b/tabelas/2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\certidaodoisjs-portfolio\tabelas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Acadêmico Juliano Zanoni\Engenharia de Software\Projetos Engenharia\Projetos\certidaodoisjs-portfolio\tabelas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F2E4D74-3876-4F27-95FA-354F06CBE8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B9E551A-5CE7-4494-97ED-58E301CB8B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{64080E1E-AD2B-4476-9478-C4BE9F04AFE1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5007" uniqueCount="1043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5006" uniqueCount="1043">
   <si>
     <t>INSCRICAO</t>
   </si>
@@ -26520,9 +26520,6 @@
       <c r="F1000" t="s">
         <v>13</v>
       </c>
-      <c r="G1000" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="1001" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1001" s="1" t="s">

--- a/tabelas/2026.xlsx
+++ b/tabelas/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Acadêmico Juliano Zanoni\Engenharia de Software\Projetos Engenharia\Projetos\certidaodoisjs-portfolio\tabelas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B9E551A-5CE7-4494-97ED-58E301CB8B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03ACD122-6B48-44B3-8989-7CE53FE8C106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{64080E1E-AD2B-4476-9478-C4BE9F04AFE1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5006" uniqueCount="1043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5007" uniqueCount="1043">
   <si>
     <t>INSCRICAO</t>
   </si>
@@ -26515,10 +26515,13 @@
         <v>2026</v>
       </c>
       <c r="E1000" s="3">
-        <v>0</v>
+        <v>589.55999999999995</v>
       </c>
       <c r="F1000" t="s">
         <v>13</v>
+      </c>
+      <c r="G1000" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="1001" spans="1:7" x14ac:dyDescent="0.25">
